--- a/event_registration_forms/031_treasury_innovation_forum_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/031_treasury_innovation_forum_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'attendee',_'label':_'attendee'}</t>
+          <t>attendee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'attendee', 'label': 'Attendee'}</t>
+          <t>Attendee</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'speaker',_'label':_'speaker'}</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'speaker', 'label': 'Speaker'}</t>
+          <t>Speaker</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'exhibitor',_'label':_'exhibitor'}</t>
+          <t>exhibitor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'exhibitor', 'label': 'Exhibitor'}</t>
+          <t>Exhibitor</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'online_payment',_'label':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'online_payment', 'label': 'Online Payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'offline_payment',_'label':_'offline_payment'}</t>
+          <t>offline_payment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'offline_payment', 'label': 'Offline Payment'}</t>
+          <t>Offline Payment</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'no_payment',_'label':_'no_payment'}</t>
+          <t>no_payment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'no_payment', 'label': 'No Payment'}</t>
+          <t>No Payment</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'visa',_'label':_'visa'}</t>
+          <t>visa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'visa', 'label': 'Visa'}</t>
+          <t>Visa</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'mastercard',_'label':_'mastercard'}</t>
+          <t>mastercard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'mastercard', 'label': 'Mastercard'}</t>
+          <t>Mastercard</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'amex',_'label':_'amex'}</t>
+          <t>amex</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'amex', 'label': 'Amex'}</t>
+          <t>Amex</t>
         </is>
       </c>
     </row>
